--- a/public/ModeleImportationLivraisonsExcedentaires.xlsx
+++ b/public/ModeleImportationLivraisonsExcedentaires.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\LENOVO\Documents\magcarburant\public\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9907BCE0-9BDF-4C44-86CC-67C91F1266BE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B11BB110-ADA5-46BD-BB6D-F809FB963A7E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -90,9 +90,6 @@
     <t>DATE VENTE</t>
   </si>
   <si>
-    <t>QUANTITE M3</t>
-  </si>
-  <si>
     <t>PRIX UNITAIRE</t>
   </si>
   <si>
@@ -100,6 +97,9 @@
   </si>
   <si>
     <t>MODELE D'IMPORTATION DES LIVRAISONS EXCEDENTAIRES</t>
+  </si>
+  <si>
+    <t>LATA</t>
   </si>
 </sst>
 </file>
@@ -230,7 +230,7 @@
     <tableColumn id="4" xr3:uid="{C5EABC09-E73C-47CB-B09B-E1E47D6D0823}" name="BON DE LIVRAISON"/>
     <tableColumn id="5" xr3:uid="{D932CCAA-A9B2-4899-9FB0-33A8F4DF4C61}" name="PROGRAMME DE LIVRAISON"/>
     <tableColumn id="7" xr3:uid="{0BF0FD66-DB30-4762-89EA-EAF220B67E49}" name="CLIENT"/>
-    <tableColumn id="8" xr3:uid="{72DFB174-8B8E-4C20-9370-363A28147B56}" name="QUANTITE M3"/>
+    <tableColumn id="8" xr3:uid="{72DFB174-8B8E-4C20-9370-363A28147B56}" name="LATA"/>
     <tableColumn id="9" xr3:uid="{78FD30C1-9524-4772-A5BB-879876CFD2E9}" name="PRIX UNITAIRE"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
@@ -556,16 +556,16 @@
         <v>5</v>
       </c>
       <c r="I1" t="s">
+        <v>23</v>
+      </c>
+      <c r="J1" t="s">
         <v>20</v>
-      </c>
-      <c r="J1" t="s">
-        <v>21</v>
       </c>
     </row>
     <row r="2" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="F2" s="3"/>
       <c r="M2" s="6" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="N2" s="6"/>
       <c r="O2" s="6"/>
@@ -770,25 +770,25 @@
     <row r="21" spans="6:15" x14ac:dyDescent="0.3">
       <c r="F21" s="3"/>
       <c r="M21" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="N21" s="2" t="s">
         <v>14</v>
       </c>
       <c r="O21" s="1" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="22" spans="6:15" x14ac:dyDescent="0.3">
       <c r="F22" s="3"/>
       <c r="M22" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="N22" s="2" t="s">
         <v>14</v>
       </c>
       <c r="O22" s="1" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="23" spans="6:15" ht="15" customHeight="1" x14ac:dyDescent="0.3">
